--- a/harmonized_tables_advp/from_31497858_table1_v1.xlsx
+++ b/harmonized_tables_advp/from_31497858_table1_v1.xlsx
@@ -668,12 +668,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -683,28 +683,24 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -717,7 +713,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -800,12 +796,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -815,28 +811,24 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -849,7 +841,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -932,12 +924,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,28 +939,24 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -981,7 +969,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1064,12 +1052,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,28 +1067,24 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -1113,7 +1097,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1196,12 +1180,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1211,28 +1195,24 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -1245,7 +1225,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1328,12 +1308,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1343,28 +1323,24 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -1377,7 +1353,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1460,12 +1436,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1475,28 +1451,24 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -1509,7 +1481,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1592,12 +1564,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1607,28 +1579,24 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1641,7 +1609,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1724,12 +1692,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1739,28 +1707,24 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1773,7 +1737,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1856,12 +1820,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1871,28 +1835,24 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -1905,7 +1865,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1988,12 +1948,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2003,28 +1963,24 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -2037,7 +1993,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2120,12 +2076,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2135,28 +2091,24 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -2169,7 +2121,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2252,12 +2204,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2267,28 +2219,24 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -2301,7 +2249,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2384,12 +2332,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2399,28 +2347,24 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -2433,7 +2377,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2516,12 +2460,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2531,28 +2475,24 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -2565,7 +2505,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2648,12 +2588,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2663,12 +2603,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2684,7 +2624,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -2697,7 +2637,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2780,12 +2720,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2795,12 +2735,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2816,7 +2756,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -2829,7 +2769,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2912,12 +2852,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2927,12 +2867,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2948,7 +2888,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -2961,7 +2901,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -3044,12 +2984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3059,28 +2999,24 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -3093,7 +3029,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -3176,12 +3112,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3191,28 +3127,24 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -3225,7 +3157,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3308,12 +3240,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Meta-analysis</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3323,28 +3255,24 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>logistic regression (with covariates)</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>ADGC;AGES</t>
-        </is>
-      </c>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -3357,7 +3285,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>European ancestry</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
